--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-01-2026.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/25mm-celotex-tb4025-pir-insulation-board-2400x1200mm-14-p.asp</t>
+          <t>£9.70</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/30mm-celotex-tb4030-pir-insulation-board-2400x1200mm-185-p.asp</t>
+          <t>£11.09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£14.01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/50mm-celotex-ga4050-pir--insulation-board-2400x1200mm-12-p.asp</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/60mm-celotex-ga4060-pir-insulation-board-2400x1200mm-1563-p.asp</t>
+          <t>£18.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/70mm-celotex-ga4070-pir-insulation-board-2400x1200mm-709-p.asp</t>
+          <t>£20.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/75mm-celotex-ga4075-pir-insulation-board-2400x1200mm-11-p.asp</t>
+          <t>£20.30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1150,7 +1150,36 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>£20.13</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.925
+  (Session info: chrome=143.0.7499.170)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6245488d5
+	0x7ff624548930
+	0x7ff62432165d
+	0x7ff62430e847
+	0x7ff62430e5bd
+	0x7ff62430c20a
+	0x7ff62430cbcf
+	0x7ff62431bb8a
+	0x7ff62433223f
+	0x7ff62433940a
+	0x7ff62430d375
+	0x7ff624331df2
+	0x7ff6243cb080
+	0x7ff62436ac29
+	0x7ff62436ba93
+	0x7ff624860620
+	0x7ff62485af60
+	0x7ff6248796c6
+	0x7ff624565dd4
+	0x7ff62456ed7c
+	0x7ff624551ff4
+	0x7ff6245521a5
+	0x7ff624537ed2
+	0x7ff95a05e8d7
+	0x7ff95b68c53c
+</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1202,7 +1231,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/80mm-celotex-ga4080-pir-insulation-board-2400x1200mm-1710-p.asp</t>
+          <t>£23.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1294,7 +1323,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/90mm-celotex-ga4090-pir-insulation-board-2400x1200mm-1705-p.asp</t>
+          <t>£25.40</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,7 +1415,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£25.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1570,7 +1599,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/120mm-celotex-xr4120-pir-insulation-board-2400x1200mm-17-p.asp</t>
+          <t>£30.40</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1662,7 +1691,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/130mm-celotex-xr4130-pir-insulation-board-2400x1200mm-2348-p.asp</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1692,7 +1721,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£81.55</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1754,7 +1783,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/140mm-celotex-xr4140-pir-insulation-board-2400x1200mm-19-p.asp</t>
+          <t>£37.79</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1784,7 +1813,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£86.21</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1846,7 +1875,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/150mm-celotex-xr4150-pir-insulation-board-2400x1200mm-20-p.asp</t>
+          <t>£37.32</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1876,7 +1905,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£89.87</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1938,7 +1967,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/165mm-celotex-xr4165-pir-insulation-board-2400x1200mm-pack-of-12-boards-2570-p.asp</t>
+          <t>£690.66</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2030,7 +2059,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/200mm-celotex-xr4200-pir-insulation-board-2400x1200mm-pack-of-12-boards-2577-p.asp</t>
+          <t>£867.05</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2122,7 +2151,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/375mm-celotex-pl4025-pir-insulated-plasterboard---12m-x-24m-70-p.asp</t>
+          <t>£25.50</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2214,7 +2243,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/525mm-celotex-pl4040-pir-insulated-plasterboard---12m-x-24m-72-p.asp</t>
+          <t>£31.05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2306,7 +2335,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/625mm-celotex-pl4050-pir-insulated-plasterboard---12m-x-24m-610-p.asp</t>
+          <t>£34.10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2398,7 +2427,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/725mm-celotex-pl4060-pir-insulated-plasterboard---12m-x-24m-2336-p.asp</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2490,7 +2519,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://onlineinsulation-sales.com/50mm-celotex-cw4050-50mm-cavity-insulation-1200-x-450mm---11-boards-per-pack-726-p.asp</t>
+          <t>£43.55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2582,7 +2611,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£47.03</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2766,7 +2795,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£43.05</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2858,7 +2887,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£1107.2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2950,7 +2979,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£1242.08</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3042,7 +3071,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£1177.28</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-01-2026.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£23.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£27.67</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -695,7 +695,36 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>£11.40</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.441
+  (Session info: chrome=143.0.7499.170)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff625fa88d5
+	0x7ff625fa8930
+	0x7ff625d8165d
+	0x7ff625d6e847
+	0x7ff625d6e5bd
+	0x7ff625d6c20a
+	0x7ff625d6cbcf
+	0x7ff625d7bb8a
+	0x7ff625d9223f
+	0x7ff625d9940a
+	0x7ff625d6d375
+	0x7ff625d91df2
+	0x7ff625e2b080
+	0x7ff625dcac29
+	0x7ff625dcba93
+	0x7ff6262c0620
+	0x7ff6262baf60
+	0x7ff6262d96c6
+	0x7ff625fc5dd4
+	0x7ff625fced7c
+	0x7ff625fb1ff4
+	0x7ff625fb21a5
+	0x7ff625f97ed2
+	0x7ff95a05e8d7
+	0x7ff95b68c53c
+</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -772,7 +801,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -864,7 +893,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>£32.42</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -956,7 +985,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>£39.12</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1048,7 +1077,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>£46.64</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1140,7 +1169,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>£46.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1150,43 +1179,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.925
+          <t>£20.13</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.757
   (Session info: chrome=143.0.7499.170)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6245488d5
-	0x7ff624548930
-	0x7ff62432165d
-	0x7ff62430e847
-	0x7ff62430e5bd
-	0x7ff62430c20a
-	0x7ff62430cbcf
-	0x7ff62431bb8a
-	0x7ff62433223f
-	0x7ff62433940a
-	0x7ff62430d375
-	0x7ff624331df2
-	0x7ff6243cb080
-	0x7ff62436ac29
-	0x7ff62436ba93
-	0x7ff624860620
-	0x7ff62485af60
-	0x7ff6248796c6
-	0x7ff624565dd4
-	0x7ff62456ed7c
-	0x7ff624551ff4
-	0x7ff6245521a5
-	0x7ff624537ed2
+	0x7ff625fa88d5
+	0x7ff625fa8930
+	0x7ff625d8165d
+	0x7ff625d6e847
+	0x7ff625d6e5bd
+	0x7ff625d6c20a
+	0x7ff625d6cbcf
+	0x7ff625d7bb8a
+	0x7ff625d9223f
+	0x7ff625d9940a
+	0x7ff625d6d375
+	0x7ff625d91df2
+	0x7ff625e2b080
+	0x7ff625dcac29
+	0x7ff625dcba93
+	0x7ff6262c0620
+	0x7ff6262baf60
+	0x7ff6262d96c6
+	0x7ff625fc5dd4
+	0x7ff625fced7c
+	0x7ff625fb1ff4
+	0x7ff625fb21a5
+	0x7ff625f97ed2
 	0x7ff95a05e8d7
 	0x7ff95b68c53c
 </t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>£20.16</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>£21.34</t>
@@ -1261,7 +1290,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>£51.7</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1353,7 +1382,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>£57.31</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1445,7 +1474,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£49.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1721,7 +1750,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>£81.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1813,7 +1842,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>£86.21</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1905,7 +1934,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£89.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2034,19 +2063,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>£890.00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>£890.00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>£890.00</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>£895.00</t>
@@ -2054,7 +2083,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>£1407.24</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2104,7 +2133,36 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.952
+  (Session info: chrome=143.0.7499.170)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff625fa88d5
+	0x7ff625fa8930
+	0x7ff625d8165d
+	0x7ff625d6e847
+	0x7ff625d6e5bd
+	0x7ff625d6c20a
+	0x7ff625d6cbcf
+	0x7ff625d7bb8a
+	0x7ff625d9223f
+	0x7ff625d9940a
+	0x7ff625d6d375
+	0x7ff625d91df2
+	0x7ff625e2b080
+	0x7ff625dcac29
+	0x7ff625dcba93
+	0x7ff6262c0620
+	0x7ff6262baf60
+	0x7ff6262d96c6
+	0x7ff625fc5dd4
+	0x7ff625fced7c
+	0x7ff625fb1ff4
+	0x7ff625fb21a5
+	0x7ff625f97ed2
+	0x7ff95a05e8d7
+	0x7ff95b68c53c
+</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2181,7 +2239,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>£51.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2196,7 +2254,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>£26.90</t>
+          <t>£34.00</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2273,7 +2331,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>£59.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2365,7 +2423,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£79.58</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2457,7 +2515,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>£70.18</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
